--- a/prep_and_checklists/Soloman  /PREPLIST_Soloman  _01-21-2026_0.xlsx
+++ b/prep_and_checklists/Soloman  /PREPLIST_Soloman  _01-21-2026_0.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Soloman  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3774F2B4-27C9-BA4A-96AF-F49DDF0B64B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B2EE31-C4D8-7044-985D-51778ADE974C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prep_sheet" sheetId="1" r:id="rId1"/>
     <sheet name="order_sheet" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -844,7 +857,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="29.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.25">
